--- a/examples/outputs/Birgo RR Exhibits - Lyndon Crossingsv08.31.26.xlsx
+++ b/examples/outputs/Birgo RR Exhibits - Lyndon Crossingsv08.31.26.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Unit Mix based on # of Beds" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Pres. Rent Roll" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="OneLineRR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Source" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="15">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="#0\ &quot;Units&quot;"/>
     <numFmt numFmtId="165" formatCode="#\ &quot;Units&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0\ &quot;SF&quot;"/>
@@ -36,6 +37,9 @@
     <numFmt numFmtId="176" formatCode="mm\/dd\/yyyy"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="#,##0.00;[Red]#,##0.00"/>
+    <numFmt numFmtId="180" formatCode="#,##0.00;\(#,##0.00\)"/>
+    <numFmt numFmtId="181" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -153,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -387,6 +391,11 @@
     <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -11498,4 +11507,3815 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:AL90"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.5703125" customWidth="1" min="1" max="1"/>
+    <col width="10.7109375" customWidth="1" min="4" max="4"/>
+    <col width="13.5703125" customWidth="1" min="5" max="5"/>
+    <col width="10.7109375" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Rent Roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Unit Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bldg-Unit</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Unit Type</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SQFT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Unit Status</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Resident</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Move-In</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Lease Start</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Lease End</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Expected Move-Out</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Market Rent</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Scheduled Charges</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Deposit Held</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1200-1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D8" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Vacant Rented Not Ready</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="K8" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="L8" s="88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1200-2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D9" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jarboe, Rebekah</t>
+        </is>
+      </c>
+      <c r="G9" s="89" t="n">
+        <v>46204</v>
+      </c>
+      <c r="H9" s="89" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I9" s="89" t="n">
+        <v>46572</v>
+      </c>
+      <c r="K9" s="88" t="n">
+        <v>1109</v>
+      </c>
+      <c r="L9" s="88" t="n">
+        <v>1216</v>
+      </c>
+      <c r="M9" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1200-3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D10" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Wallace, Christina</t>
+        </is>
+      </c>
+      <c r="G10" s="89" t="n">
+        <v>46179</v>
+      </c>
+      <c r="H10" s="89" t="n">
+        <v>46179</v>
+      </c>
+      <c r="I10" s="89" t="n">
+        <v>46579</v>
+      </c>
+      <c r="K10" s="88" t="n">
+        <v>1214</v>
+      </c>
+      <c r="L10" s="88" t="n">
+        <v>1214</v>
+      </c>
+      <c r="M10" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1200-4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D11" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Strait, Conner</t>
+        </is>
+      </c>
+      <c r="G11" s="89" t="n">
+        <v>45955</v>
+      </c>
+      <c r="H11" s="89" t="n">
+        <v>45955</v>
+      </c>
+      <c r="I11" s="89" t="n">
+        <v>46502</v>
+      </c>
+      <c r="K11" s="88" t="n">
+        <v>1231</v>
+      </c>
+      <c r="L11" s="88" t="n">
+        <v>1099</v>
+      </c>
+      <c r="M11" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1200-5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D12" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Moore, Torey</t>
+        </is>
+      </c>
+      <c r="G12" s="89" t="n">
+        <v>43922</v>
+      </c>
+      <c r="H12" s="89" t="n">
+        <v>46143</v>
+      </c>
+      <c r="I12" s="89" t="n">
+        <v>46572</v>
+      </c>
+      <c r="K12" s="88" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L12" s="88" t="n">
+        <v>1078</v>
+      </c>
+      <c r="M12" s="88" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1200-6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D13" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Styer, Hannah</t>
+        </is>
+      </c>
+      <c r="G13" s="89" t="n">
+        <v>42928</v>
+      </c>
+      <c r="H13" s="89" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I13" s="89" t="n">
+        <v>46663</v>
+      </c>
+      <c r="K13" s="88" t="n">
+        <v>1165</v>
+      </c>
+      <c r="L13" s="88" t="n">
+        <v>1240</v>
+      </c>
+      <c r="M13" s="88" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1201-1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D14" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Notice Unrented</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Johnson, Christopher</t>
+        </is>
+      </c>
+      <c r="G14" s="89" t="n">
+        <v>44494</v>
+      </c>
+      <c r="H14" s="89" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I14" s="89" t="n">
+        <v>46271</v>
+      </c>
+      <c r="J14" s="89" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K14" s="88" t="n">
+        <v>1291</v>
+      </c>
+      <c r="L14" s="88" t="n">
+        <v>1299</v>
+      </c>
+      <c r="M14" s="88" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1201-2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D15" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mabinda, Marie</t>
+        </is>
+      </c>
+      <c r="G15" s="89" t="n">
+        <v>45178</v>
+      </c>
+      <c r="H15" s="89" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I15" s="89" t="n">
+        <v>46481</v>
+      </c>
+      <c r="K15" s="88" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L15" s="88" t="n">
+        <v>1096</v>
+      </c>
+      <c r="M15" s="88" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1201-3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D16" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Thornton, Roderick</t>
+        </is>
+      </c>
+      <c r="G16" s="89" t="n">
+        <v>42461</v>
+      </c>
+      <c r="H16" s="89" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I16" s="89" t="n">
+        <v>46509</v>
+      </c>
+      <c r="K16" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L16" s="88" t="n">
+        <v>1108</v>
+      </c>
+      <c r="M16" s="88" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1201-4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D17" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Amback, Brian</t>
+        </is>
+      </c>
+      <c r="G17" s="89" t="n">
+        <v>45164</v>
+      </c>
+      <c r="H17" s="89" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I17" s="89" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K17" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L17" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M17" s="88" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1201-5</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D18" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lozano, Yajaira</t>
+        </is>
+      </c>
+      <c r="G18" s="89" t="n">
+        <v>45773</v>
+      </c>
+      <c r="H18" s="89" t="n">
+        <v>46202</v>
+      </c>
+      <c r="I18" s="89" t="n">
+        <v>46600</v>
+      </c>
+      <c r="K18" s="88" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L18" s="88" t="n">
+        <v>1185</v>
+      </c>
+      <c r="M18" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1201-6</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D19" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jackson, Bryonnie</t>
+        </is>
+      </c>
+      <c r="G19" s="89" t="n">
+        <v>46153</v>
+      </c>
+      <c r="H19" s="89" t="n">
+        <v>46153</v>
+      </c>
+      <c r="I19" s="89" t="n">
+        <v>46614</v>
+      </c>
+      <c r="K19" s="88" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L19" s="88" t="n">
+        <v>1180</v>
+      </c>
+      <c r="M19" s="88" t="n">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1202-1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D20" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Vacant Rented Ready</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="K20" s="88" t="n">
+        <v>1242</v>
+      </c>
+      <c r="L20" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1202-2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D21" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Broadwater, Eric</t>
+        </is>
+      </c>
+      <c r="G21" s="89" t="n">
+        <v>46137</v>
+      </c>
+      <c r="H21" s="89" t="n">
+        <v>46137</v>
+      </c>
+      <c r="I21" s="89" t="n">
+        <v>46628</v>
+      </c>
+      <c r="K21" s="88" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L21" s="88" t="n">
+        <v>1118</v>
+      </c>
+      <c r="M21" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1202-3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D22" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kavanah, Ryan</t>
+        </is>
+      </c>
+      <c r="G22" s="89" t="n">
+        <v>45219</v>
+      </c>
+      <c r="H22" s="89" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I22" s="89" t="n">
+        <v>46509</v>
+      </c>
+      <c r="K22" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L22" s="88" t="n">
+        <v>1145</v>
+      </c>
+      <c r="M22" s="88" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1202-4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D23" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dunigan, Sydney</t>
+        </is>
+      </c>
+      <c r="G23" s="89" t="n">
+        <v>45877</v>
+      </c>
+      <c r="H23" s="89" t="n">
+        <v>46244</v>
+      </c>
+      <c r="I23" s="89" t="n">
+        <v>46551</v>
+      </c>
+      <c r="K23" s="88" t="n">
+        <v>1177</v>
+      </c>
+      <c r="L23" s="88" t="n">
+        <v>1275</v>
+      </c>
+      <c r="M23" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1202-5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D24" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bohning, Kimberly</t>
+        </is>
+      </c>
+      <c r="G24" s="89" t="n">
+        <v>45840</v>
+      </c>
+      <c r="H24" s="89" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I24" s="89" t="n">
+        <v>46488</v>
+      </c>
+      <c r="K24" s="88" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L24" s="88" t="n">
+        <v>1218</v>
+      </c>
+      <c r="M24" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1202-6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D25" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Howes, Justin</t>
+        </is>
+      </c>
+      <c r="G25" s="89" t="n">
+        <v>45426</v>
+      </c>
+      <c r="H25" s="89" t="n">
+        <v>46176</v>
+      </c>
+      <c r="I25" s="89" t="n">
+        <v>46544</v>
+      </c>
+      <c r="K25" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L25" s="88" t="n">
+        <v>1231</v>
+      </c>
+      <c r="M25" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1209-1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D26" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Shearer, Roy (Keith)</t>
+        </is>
+      </c>
+      <c r="G26" s="89" t="n">
+        <v>43525</v>
+      </c>
+      <c r="H26" s="89" t="n">
+        <v>46181</v>
+      </c>
+      <c r="I26" s="89" t="n">
+        <v>46579</v>
+      </c>
+      <c r="K26" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L26" s="88" t="n">
+        <v>1099</v>
+      </c>
+      <c r="M26" s="88" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1209-2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D27" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VanDyke, Benjamin</t>
+        </is>
+      </c>
+      <c r="G27" s="89" t="n">
+        <v>46076</v>
+      </c>
+      <c r="H27" s="89" t="n">
+        <v>46076</v>
+      </c>
+      <c r="I27" s="89" t="n">
+        <v>46621</v>
+      </c>
+      <c r="K27" s="88" t="n">
+        <v>1160</v>
+      </c>
+      <c r="L27" s="88" t="n">
+        <v>1068</v>
+      </c>
+      <c r="M27" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1209-3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D28" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Maly, Mary</t>
+        </is>
+      </c>
+      <c r="G28" s="89" t="n">
+        <v>43792</v>
+      </c>
+      <c r="H28" s="89" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I28" s="89" t="n">
+        <v>46544</v>
+      </c>
+      <c r="K28" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L28" s="88" t="n">
+        <v>1146</v>
+      </c>
+      <c r="M28" s="88" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1209-4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D29" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Purvis, Jason</t>
+        </is>
+      </c>
+      <c r="G29" s="89" t="n">
+        <v>45582</v>
+      </c>
+      <c r="H29" s="89" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I29" s="89" t="n">
+        <v>46509</v>
+      </c>
+      <c r="K29" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L29" s="88" t="n">
+        <v>1212</v>
+      </c>
+      <c r="M29" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1209-5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D30" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Powers, Neika</t>
+        </is>
+      </c>
+      <c r="G30" s="89" t="n">
+        <v>43586</v>
+      </c>
+      <c r="H30" s="89" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I30" s="89" t="n">
+        <v>46362</v>
+      </c>
+      <c r="K30" s="88" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L30" s="88" t="n">
+        <v>1137</v>
+      </c>
+      <c r="M30" s="88" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1209-6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D31" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Screen, Joseph</t>
+        </is>
+      </c>
+      <c r="G31" s="89" t="n">
+        <v>45804</v>
+      </c>
+      <c r="H31" s="89" t="n">
+        <v>46174</v>
+      </c>
+      <c r="I31" s="89" t="n">
+        <v>46600</v>
+      </c>
+      <c r="K31" s="88" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L31" s="88" t="n">
+        <v>1195</v>
+      </c>
+      <c r="M31" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1211-1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D32" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Reasons, Justin</t>
+        </is>
+      </c>
+      <c r="G32" s="89" t="n">
+        <v>44470</v>
+      </c>
+      <c r="H32" s="89" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I32" s="89" t="n">
+        <v>46481</v>
+      </c>
+      <c r="K32" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L32" s="88" t="n">
+        <v>1125</v>
+      </c>
+      <c r="M32" s="88" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1211-2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D33" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Smith, Stuart</t>
+        </is>
+      </c>
+      <c r="G33" s="89" t="n">
+        <v>46157</v>
+      </c>
+      <c r="H33" s="89" t="n">
+        <v>46157</v>
+      </c>
+      <c r="I33" s="89" t="n">
+        <v>46586</v>
+      </c>
+      <c r="K33" s="88" t="n">
+        <v>1199</v>
+      </c>
+      <c r="L33" s="88" t="n">
+        <v>1199</v>
+      </c>
+      <c r="M33" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1211-3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D34" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Watson, Mhairi</t>
+        </is>
+      </c>
+      <c r="G34" s="89" t="n">
+        <v>45871</v>
+      </c>
+      <c r="H34" s="89" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I34" s="89" t="n">
+        <v>46544</v>
+      </c>
+      <c r="K34" s="88" t="n">
+        <v>1221</v>
+      </c>
+      <c r="L34" s="88" t="n">
+        <v>1296</v>
+      </c>
+      <c r="M34" s="88" t="n">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1211-4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D35" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Selter, Aundrea</t>
+        </is>
+      </c>
+      <c r="G35" s="89" t="n">
+        <v>46118</v>
+      </c>
+      <c r="H35" s="89" t="n">
+        <v>46118</v>
+      </c>
+      <c r="I35" s="89" t="n">
+        <v>46607</v>
+      </c>
+      <c r="K35" s="88" t="n">
+        <v>1174</v>
+      </c>
+      <c r="L35" s="88" t="n">
+        <v>1140</v>
+      </c>
+      <c r="M35" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1211-5</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D36" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Vacant Unrented Ready</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="K36" s="88" t="n">
+        <v>1153</v>
+      </c>
+      <c r="L36" s="88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1211-6</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D37" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Presley, Allen</t>
+        </is>
+      </c>
+      <c r="G37" s="89" t="n">
+        <v>44348</v>
+      </c>
+      <c r="H37" s="89" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I37" s="89" t="n">
+        <v>46544</v>
+      </c>
+      <c r="K37" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L37" s="88" t="n">
+        <v>973</v>
+      </c>
+      <c r="M37" s="88" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1212-1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D38" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Johnson, Marvet</t>
+        </is>
+      </c>
+      <c r="G38" s="89" t="n">
+        <v>44228</v>
+      </c>
+      <c r="H38" s="89" t="n">
+        <v>46146</v>
+      </c>
+      <c r="I38" s="89" t="n">
+        <v>46516</v>
+      </c>
+      <c r="K38" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L38" s="88" t="n">
+        <v>1131</v>
+      </c>
+      <c r="M38" s="88" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1212-2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D39" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Russell, Marie</t>
+        </is>
+      </c>
+      <c r="G39" s="89" t="n">
+        <v>45199</v>
+      </c>
+      <c r="H39" s="89" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I39" s="89" t="n">
+        <v>46481</v>
+      </c>
+      <c r="K39" s="88" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L39" s="88" t="n">
+        <v>1096</v>
+      </c>
+      <c r="M39" s="88" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1212-3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D40" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Culp, Bethany</t>
+        </is>
+      </c>
+      <c r="G40" s="89" t="n">
+        <v>45976</v>
+      </c>
+      <c r="H40" s="89" t="n">
+        <v>45976</v>
+      </c>
+      <c r="I40" s="89" t="n">
+        <v>46523</v>
+      </c>
+      <c r="K40" s="88" t="n">
+        <v>1235</v>
+      </c>
+      <c r="L40" s="88" t="n">
+        <v>1184</v>
+      </c>
+      <c r="M40" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1212-4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D41" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Accuardi, John</t>
+        </is>
+      </c>
+      <c r="G41" s="89" t="n">
+        <v>43957</v>
+      </c>
+      <c r="H41" s="89" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I41" s="89" t="n">
+        <v>46635</v>
+      </c>
+      <c r="K41" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L41" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M41" s="88" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1212-5</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D42" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Swanson, Brandon</t>
+        </is>
+      </c>
+      <c r="G42" s="89" t="n">
+        <v>43980</v>
+      </c>
+      <c r="H42" s="89" t="n">
+        <v>46174</v>
+      </c>
+      <c r="I42" s="89" t="n">
+        <v>46635</v>
+      </c>
+      <c r="K42" s="88" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L42" s="88" t="n">
+        <v>1178</v>
+      </c>
+      <c r="M42" s="88" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1212-6</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D43" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Green, Latania</t>
+        </is>
+      </c>
+      <c r="G43" s="89" t="n">
+        <v>46155</v>
+      </c>
+      <c r="H43" s="89" t="n">
+        <v>46155</v>
+      </c>
+      <c r="I43" s="89" t="n">
+        <v>46586</v>
+      </c>
+      <c r="K43" s="88" t="n">
+        <v>1206</v>
+      </c>
+      <c r="L43" s="88" t="n">
+        <v>1206</v>
+      </c>
+      <c r="M43" s="88" t="n">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1213-1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D44" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>lockard, catherine</t>
+        </is>
+      </c>
+      <c r="G44" s="89" t="n">
+        <v>46248</v>
+      </c>
+      <c r="H44" s="89" t="n">
+        <v>46248</v>
+      </c>
+      <c r="I44" s="89" t="n">
+        <v>46796</v>
+      </c>
+      <c r="K44" s="88" t="n">
+        <v>1256</v>
+      </c>
+      <c r="L44" s="88" t="n">
+        <v>1298</v>
+      </c>
+      <c r="M44" s="88" t="n">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1213-2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D45" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Vacant Unrented Ready</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="K45" s="88" t="n">
+        <v>1123</v>
+      </c>
+      <c r="L45" s="88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1213-3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D46" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kelly, John</t>
+        </is>
+      </c>
+      <c r="G46" s="89" t="n">
+        <v>46218</v>
+      </c>
+      <c r="H46" s="89" t="n">
+        <v>46218</v>
+      </c>
+      <c r="I46" s="89" t="n">
+        <v>46495</v>
+      </c>
+      <c r="K46" s="88" t="n">
+        <v>1225</v>
+      </c>
+      <c r="L46" s="88" t="n">
+        <v>1226</v>
+      </c>
+      <c r="M46" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1213-4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D47" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Anderson, Cristopher</t>
+        </is>
+      </c>
+      <c r="G47" s="89" t="n">
+        <v>46129</v>
+      </c>
+      <c r="H47" s="89" t="n">
+        <v>46129</v>
+      </c>
+      <c r="I47" s="89" t="n">
+        <v>46621</v>
+      </c>
+      <c r="K47" s="88" t="n">
+        <v>1155</v>
+      </c>
+      <c r="L47" s="88" t="n">
+        <v>1152</v>
+      </c>
+      <c r="M47" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1213-5</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D48" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vuolo, Matthew</t>
+        </is>
+      </c>
+      <c r="G48" s="89" t="n">
+        <v>45884</v>
+      </c>
+      <c r="H48" s="89" t="n">
+        <v>46251</v>
+      </c>
+      <c r="I48" s="89" t="n">
+        <v>46649</v>
+      </c>
+      <c r="K48" s="88" t="n">
+        <v>1305</v>
+      </c>
+      <c r="L48" s="88" t="n">
+        <v>1176</v>
+      </c>
+      <c r="M48" s="88" t="n">
+        <v>553.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1213-6</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D49" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Goodman EMPLOYEE, Lorie</t>
+        </is>
+      </c>
+      <c r="G49" s="89" t="n">
+        <v>45966</v>
+      </c>
+      <c r="H49" s="89" t="n">
+        <v>45966</v>
+      </c>
+      <c r="I49" s="89" t="n">
+        <v>46516</v>
+      </c>
+      <c r="K49" s="88" t="n">
+        <v>1364</v>
+      </c>
+      <c r="L49" s="88" t="n">
+        <v>1215</v>
+      </c>
+      <c r="M49" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1215-1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D50" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Riesen, Evan</t>
+        </is>
+      </c>
+      <c r="G50" s="89" t="n">
+        <v>46102</v>
+      </c>
+      <c r="H50" s="89" t="n">
+        <v>46102</v>
+      </c>
+      <c r="I50" s="89" t="n">
+        <v>46593</v>
+      </c>
+      <c r="K50" s="88" t="n">
+        <v>1099</v>
+      </c>
+      <c r="L50" s="88" t="n">
+        <v>1099</v>
+      </c>
+      <c r="M50" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1215-2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D51" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Bennett, Octavia</t>
+        </is>
+      </c>
+      <c r="G51" s="89" t="n">
+        <v>45422</v>
+      </c>
+      <c r="H51" s="89" t="n">
+        <v>46174</v>
+      </c>
+      <c r="I51" s="89" t="n">
+        <v>46635</v>
+      </c>
+      <c r="K51" s="88" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L51" s="88" t="n">
+        <v>1198</v>
+      </c>
+      <c r="M51" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1215-3</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D52" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Wyatt, Daquan</t>
+        </is>
+      </c>
+      <c r="G52" s="89" t="n">
+        <v>45973</v>
+      </c>
+      <c r="H52" s="89" t="n">
+        <v>45973</v>
+      </c>
+      <c r="I52" s="89" t="n">
+        <v>46523</v>
+      </c>
+      <c r="K52" s="88" t="n">
+        <v>1233</v>
+      </c>
+      <c r="L52" s="88" t="n">
+        <v>1150</v>
+      </c>
+      <c r="M52" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1215-4</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D53" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Thomas, Kobe</t>
+        </is>
+      </c>
+      <c r="G53" s="89" t="n">
+        <v>45819</v>
+      </c>
+      <c r="H53" s="89" t="n">
+        <v>46188</v>
+      </c>
+      <c r="I53" s="89" t="n">
+        <v>46558</v>
+      </c>
+      <c r="K53" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L53" s="88" t="n">
+        <v>1228</v>
+      </c>
+      <c r="M53" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1215-5</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D54" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Vacant Rented Ready</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="K54" s="88" t="n">
+        <v>1099</v>
+      </c>
+      <c r="L54" s="88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1215-6</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D55" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Smith, Morgan</t>
+        </is>
+      </c>
+      <c r="G55" s="89" t="n">
+        <v>45919</v>
+      </c>
+      <c r="H55" s="89" t="n">
+        <v>45919</v>
+      </c>
+      <c r="I55" s="89" t="n">
+        <v>46467</v>
+      </c>
+      <c r="K55" s="88" t="n">
+        <v>1271</v>
+      </c>
+      <c r="L55" s="88" t="n">
+        <v>1099</v>
+      </c>
+      <c r="M55" s="88" t="n">
+        <v>549.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>8600-1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D56" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Howser, Lisa</t>
+        </is>
+      </c>
+      <c r="G56" s="89" t="n">
+        <v>44002</v>
+      </c>
+      <c r="H56" s="89" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I56" s="89" t="n">
+        <v>46579</v>
+      </c>
+      <c r="K56" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L56" s="88" t="n">
+        <v>1172</v>
+      </c>
+      <c r="M56" s="88" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>8600-2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D57" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Williams, Candice</t>
+        </is>
+      </c>
+      <c r="G57" s="89" t="n">
+        <v>46185</v>
+      </c>
+      <c r="H57" s="89" t="n">
+        <v>46185</v>
+      </c>
+      <c r="I57" s="89" t="n">
+        <v>46551</v>
+      </c>
+      <c r="K57" s="88" t="n">
+        <v>1151</v>
+      </c>
+      <c r="L57" s="88" t="n">
+        <v>1151</v>
+      </c>
+      <c r="M57" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>8600-3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D58" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Pineda, Drew</t>
+        </is>
+      </c>
+      <c r="G58" s="89" t="n">
+        <v>45976</v>
+      </c>
+      <c r="H58" s="89" t="n">
+        <v>45976</v>
+      </c>
+      <c r="I58" s="89" t="n">
+        <v>46285</v>
+      </c>
+      <c r="K58" s="88" t="n">
+        <v>1233</v>
+      </c>
+      <c r="L58" s="88" t="n">
+        <v>1290</v>
+      </c>
+      <c r="M58" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>8600-4</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D59" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Barker, Tavarius</t>
+        </is>
+      </c>
+      <c r="G59" s="89" t="n">
+        <v>45952</v>
+      </c>
+      <c r="H59" s="89" t="n">
+        <v>45952</v>
+      </c>
+      <c r="I59" s="89" t="n">
+        <v>46502</v>
+      </c>
+      <c r="K59" s="88" t="n">
+        <v>1263</v>
+      </c>
+      <c r="L59" s="88" t="n">
+        <v>1128</v>
+      </c>
+      <c r="M59" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>8600-5</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D60" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Notice Unrented</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Green, Elaine</t>
+        </is>
+      </c>
+      <c r="G60" s="89" t="n">
+        <v>44779</v>
+      </c>
+      <c r="H60" s="89" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I60" s="89" t="n">
+        <v>46271</v>
+      </c>
+      <c r="J60" s="89" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K60" s="88" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L60" s="88" t="n">
+        <v>1137</v>
+      </c>
+      <c r="M60" s="88" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>8600-6</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D61" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Rezk, Robert</t>
+        </is>
+      </c>
+      <c r="G61" s="89" t="n">
+        <v>45117</v>
+      </c>
+      <c r="H61" s="89" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I61" s="89" t="n">
+        <v>46544</v>
+      </c>
+      <c r="K61" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L61" s="88" t="n">
+        <v>1245</v>
+      </c>
+      <c r="M61" s="88" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>8601-1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D62" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Allen, Michael</t>
+        </is>
+      </c>
+      <c r="G62" s="89" t="n">
+        <v>45491</v>
+      </c>
+      <c r="H62" s="89" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I62" s="89" t="n">
+        <v>46544</v>
+      </c>
+      <c r="K62" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L62" s="88" t="n">
+        <v>1215</v>
+      </c>
+      <c r="M62" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>8601-2</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D63" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Beardsley, Grace</t>
+        </is>
+      </c>
+      <c r="G63" s="89" t="n">
+        <v>45080</v>
+      </c>
+      <c r="H63" s="89" t="n">
+        <v>46118</v>
+      </c>
+      <c r="I63" s="89" t="n">
+        <v>46488</v>
+      </c>
+      <c r="K63" s="88" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L63" s="88" t="n">
+        <v>1222</v>
+      </c>
+      <c r="M63" s="88" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>8601-3</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D64" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Pisacrita, Robert</t>
+        </is>
+      </c>
+      <c r="G64" s="89" t="n">
+        <v>44021</v>
+      </c>
+      <c r="H64" s="89" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I64" s="89" t="n">
+        <v>46509</v>
+      </c>
+      <c r="K64" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L64" s="88" t="n">
+        <v>1198</v>
+      </c>
+      <c r="M64" s="88" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>8601-4</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D65" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Goodloe, Cierra</t>
+        </is>
+      </c>
+      <c r="G65" s="89" t="n">
+        <v>45509</v>
+      </c>
+      <c r="H65" s="89" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I65" s="89" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K65" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L65" s="88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M65" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>8601-5</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="D66" s="87" t="n">
+        <v>860</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Lusco, Megan</t>
+        </is>
+      </c>
+      <c r="G66" s="89" t="n">
+        <v>43700</v>
+      </c>
+      <c r="H66" s="89" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I66" s="89" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K66" s="88" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L66" s="88" t="n">
+        <v>1137</v>
+      </c>
+      <c r="M66" s="88" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>8601-6</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="D67" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Sanchez, Carlos</t>
+        </is>
+      </c>
+      <c r="G67" s="89" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H67" s="89" t="n">
+        <v>45926</v>
+      </c>
+      <c r="I67" s="89" t="n">
+        <v>46474</v>
+      </c>
+      <c r="K67" s="88" t="n">
+        <v>1245</v>
+      </c>
+      <c r="L67" s="88" t="n">
+        <v>1099</v>
+      </c>
+      <c r="M67" s="88" t="n">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings Total:</t>
+        </is>
+      </c>
+      <c r="D68" s="87" t="n">
+        <v>55760</v>
+      </c>
+      <c r="K68" s="88" t="n">
+        <v>71703</v>
+      </c>
+      <c r="L68" s="88" t="n">
+        <v>64522</v>
+      </c>
+      <c r="M68" s="88" t="n">
+        <v>30334</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Status Summary</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Charge Code Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unit Count</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Charge Code</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Charge Code Type</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Status Summary - Scheduled Rent</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Status Summary - Scheduled Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="B72" s="87" t="n">
+        <v>53</v>
+      </c>
+      <c r="C72" s="90" t="n">
+        <v>0.8833333333333333</v>
+      </c>
+      <c r="D72" s="91" t="inlineStr">
+        <is>
+          <t>Ledger: Resident</t>
+        </is>
+      </c>
+      <c r="O72" s="88" t="n">
+        <v>62086</v>
+      </c>
+      <c r="P72" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Notice Unrented</t>
+        </is>
+      </c>
+      <c r="B73" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" s="90" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Amenity Rent</t>
+        </is>
+      </c>
+      <c r="E73" s="88" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="O73" s="88" t="n">
+        <v>2436</v>
+      </c>
+      <c r="P73" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Total Occupied Units</t>
+        </is>
+      </c>
+      <c r="B74" s="87" t="n">
+        <v>55</v>
+      </c>
+      <c r="C74" s="90" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Month to Month Rent</t>
+        </is>
+      </c>
+      <c r="E74" s="88" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="O74" s="88" t="n">
+        <v>64522</v>
+      </c>
+      <c r="P74" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Vacant Rented Ready</t>
+        </is>
+      </c>
+      <c r="B75" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="90" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="E75" s="88" t="n">
+        <v>61373</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="O75" s="88" t="n">
+        <v>1242</v>
+      </c>
+      <c r="P75" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Vacant Rented Not Ready</t>
+        </is>
+      </c>
+      <c r="B76" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="90" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Resident Total:</t>
+        </is>
+      </c>
+      <c r="E76" s="88" t="n">
+        <v>64522</v>
+      </c>
+      <c r="O76" s="88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Vacant Unrented Ready</t>
+        </is>
+      </c>
+      <c r="B77" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" s="90" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Total:</t>
+        </is>
+      </c>
+      <c r="E77" s="88" t="n">
+        <v>64522</v>
+      </c>
+      <c r="O77" s="88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Total Vacant Units</t>
+        </is>
+      </c>
+      <c r="B78" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="C78" s="90" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="O78" s="88" t="n">
+        <v>1242</v>
+      </c>
+      <c r="P78" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Total Rentable Units</t>
+        </is>
+      </c>
+      <c r="B79" s="87" t="n">
+        <v>60</v>
+      </c>
+      <c r="C79" s="90" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="88" t="n">
+        <v>65764</v>
+      </c>
+      <c r="P79" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Unit Type</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Rentable Units</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Occupied Units</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Market Rent</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Scheduled Charges</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Units</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Excluded Units</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - 0</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Budgeted Rent</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Market Rent</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Total Effective Rent</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Total Effective Rent With Gift</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Total Actual Rent</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Lease Rent</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Recurring Concessions</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Onetime Concessions</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Gift Incentives</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Scheduled Charges</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Scheduled Rent Sum</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Scheduled Other Sum</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Actual Charges</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Rentable Units Avg</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Rentable Unit Sqft</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Occupied Unit Sqft</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Total Unit Sqft</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Excluded Unit Sqft</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Total Lease Term</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Total Contract Length Months</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary - Total Occupied Length Months</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2x2-Gentry</t>
+        </is>
+      </c>
+      <c r="B83" s="87" t="n">
+        <v>20</v>
+      </c>
+      <c r="C83" s="87" t="n">
+        <v>17</v>
+      </c>
+      <c r="D83" s="88" t="n">
+        <v>1161.95</v>
+      </c>
+      <c r="E83" s="88" t="n">
+        <v>1153.529411764706</v>
+      </c>
+      <c r="O83" s="87" t="n">
+        <v>20</v>
+      </c>
+      <c r="P83" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="87" t="n">
+        <v>101161</v>
+      </c>
+      <c r="R83" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="87" t="n">
+        <v>23239</v>
+      </c>
+      <c r="T83" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="87" t="n">
+        <v>19610</v>
+      </c>
+      <c r="AB83" s="87" t="n">
+        <v>19610</v>
+      </c>
+      <c r="AC83" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="87" t="n">
+        <v>19574.39</v>
+      </c>
+      <c r="AE83" s="87" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF83" s="87" t="n">
+        <v>17200</v>
+      </c>
+      <c r="AG83" s="87" t="n">
+        <v>14620</v>
+      </c>
+      <c r="AH83" s="87" t="n">
+        <v>17200</v>
+      </c>
+      <c r="AI83" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="87" t="n">
+        <v>235</v>
+      </c>
+      <c r="AK83" s="87" t="n">
+        <v>235</v>
+      </c>
+      <c r="AL83" s="87" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="B84" s="87" t="n">
+        <v>40</v>
+      </c>
+      <c r="C84" s="87" t="n">
+        <v>38</v>
+      </c>
+      <c r="D84" s="88" t="n">
+        <v>1211.6</v>
+      </c>
+      <c r="E84" s="88" t="n">
+        <v>1181.894736842105</v>
+      </c>
+      <c r="O84" s="87" t="n">
+        <v>40</v>
+      </c>
+      <c r="P84" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="87" t="n">
+        <v>101161</v>
+      </c>
+      <c r="R84" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="87" t="n">
+        <v>48464</v>
+      </c>
+      <c r="T84" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="87" t="n">
+        <v>44912</v>
+      </c>
+      <c r="AB84" s="87" t="n">
+        <v>44912</v>
+      </c>
+      <c r="AC84" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="87" t="n">
+        <v>44362.1</v>
+      </c>
+      <c r="AE84" s="87" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF84" s="87" t="n">
+        <v>38560</v>
+      </c>
+      <c r="AG84" s="87" t="n">
+        <v>36632</v>
+      </c>
+      <c r="AH84" s="87" t="n">
+        <v>38560</v>
+      </c>
+      <c r="AI84" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="87" t="n">
+        <v>544</v>
+      </c>
+      <c r="AK84" s="87" t="n">
+        <v>544</v>
+      </c>
+      <c r="AL84" s="87" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Average:</t>
+        </is>
+      </c>
+      <c r="B85" s="87" t="n">
+        <v>60</v>
+      </c>
+      <c r="C85" s="87" t="n">
+        <v>55</v>
+      </c>
+      <c r="D85" s="88" t="n">
+        <v>1195.05</v>
+      </c>
+      <c r="E85" s="88" t="n">
+        <v>1173.127272727273</v>
+      </c>
+      <c r="O85" s="87" t="n">
+        <v>60</v>
+      </c>
+      <c r="P85" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="87" t="n">
+        <v>71703</v>
+      </c>
+      <c r="T85" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="87" t="n">
+        <v>64522</v>
+      </c>
+      <c r="AB85" s="87" t="n">
+        <v>64522</v>
+      </c>
+      <c r="AC85" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="87" t="n">
+        <v>63936.49</v>
+      </c>
+      <c r="AE85" s="87" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF85" s="87" t="n">
+        <v>55760</v>
+      </c>
+      <c r="AG85" s="87" t="n">
+        <v>51252</v>
+      </c>
+      <c r="AH85" s="87" t="n">
+        <v>55760</v>
+      </c>
+      <c r="AI85" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="87" t="n">
+        <v>779</v>
+      </c>
+      <c r="AK85" s="87" t="n">
+        <v>779</v>
+      </c>
+      <c r="AL85" s="87" t="n">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Future Resident Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Bldg-Unit</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Unit Type</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SQFT</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Unit Status</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Resident</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Move-In</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Lease Start</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Lease End</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Market Rent</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Actual Charges</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Scheduled Charges</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Deposit Held</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1202-1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2x2-Parkwood</t>
+        </is>
+      </c>
+      <c r="C89" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Vacant Rented Ready</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Fuller, William</t>
+        </is>
+      </c>
+      <c r="F89" s="89" t="n">
+        <v>46270</v>
+      </c>
+      <c r="G89" s="89" t="n">
+        <v>46270</v>
+      </c>
+      <c r="H89" s="89" t="n">
+        <v>46481</v>
+      </c>
+      <c r="I89" s="88" t="n">
+        <v>1242</v>
+      </c>
+      <c r="J89" s="88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="88" t="n">
+        <v>1242</v>
+      </c>
+      <c r="L89" s="88" t="n">
+        <v>500</v>
+      </c>
+      <c r="M89" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Lyndon Crossings Total:</t>
+        </is>
+      </c>
+      <c r="C90" s="87" t="n">
+        <v>964</v>
+      </c>
+      <c r="I90" s="88" t="n">
+        <v>1242</v>
+      </c>
+      <c r="J90" s="88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="88" t="n">
+        <v>1242</v>
+      </c>
+      <c r="L90" s="88" t="n">
+        <v>500</v>
+      </c>
+      <c r="M90" s="88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>